--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,6 +646,23 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R1】量化割韭菜与盘中快速崩落：该帖直接指向量化主导的快速下杀和反应时间不足，形成微观流动性与情绪风险苗头；但证据仍集中在盘中体感，未扩展为系统性风险。（来源：https://xueqiu.com/7143769715/406276234）
+【R1】银行煤炭黄金拉升后的量化反向砸盘：该帖提供了更具体的盘面传导：资源/避险方向拉升后被快速反向砸盘，说明微观流动性对方向信号的承接不足，交易者被迫面对短线T和高开低走风险。（来源：https://xueqiu.com/7143769715/406279436）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -663,6 +663,45 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】不知道说啥好。如果交易能力休息也是不错的选择。最近，农林渔牧轮动涨，石油石化煤炭天然气通胀趋势性行情， 创业板 喋喋不休... - 雪球：多项宏观和交易结构因素共同指向成长方向风险抬升，但作者表述仍以短期反弹难延续为主，未确认全面系统性风险。（来源：https://xueqiu.com/7143769715/407363126）
+【R2】如果买成长股，我还是建议10月后再看吧。等中米会谈落地。如果谈不好，反手制裁代工厂科技股，那时候基本面风险+流动性风险同... - 雪球：风险对象、条件触发和传导链清楚，构成中等风险增强；但作者同时说明这是最坏打算且政策转向仍说不清，所以不升为R3。（来源：https://xueqiu.com/7143769715/407369572）
+【W1】手握星辰摘日月。阴极阳生动乾坤。通胀趋势线。 - 雪球：该帖提供通胀线机会观察和风险钝化线索，但正文较短、缺少独立价格和资金验证，只按W1记录。（来源：https://xueqiu.com/7143769715/407407858）
+【W1】说几点政策性影响节点的事，1， 西部矿业 ，西藏税费调整，7%-10%。自然资源部最高税费就是10%。那么，这属于一次性... - 雪球：该帖有明确政策冲击、价格调整和边际缓和逻辑，但仍需要后续供需、库存和价格趋势验证，按W1记录。（来源：https://xueqiu.com/7143769715/407422888）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】利率上行的趋势性，通胀顽固性→科技承压性。 - 雪球：该帖给出明确宏观触发和科技承压传导链，但信息较短、尚未单独展开市场反馈，按中等风险增强记录。（来源：https://xueqiu.com/7143769715/407523828）
+【R2】围绕救市十字星震荡了很久了。3373-3469-3507。来回割韭菜，套路深。节奏不好就是养分。因此，需要警惕掩护出货的... - 雪球：该帖的风险对象、交易结构和传导方向清楚，风险明显增强但仍集中于科技报团和基金重仓方向，按R2记录。（来源：https://xueqiu.com/7143769715/407542311）
+【W1】北证50 开始活跃，小盘股的活跃，有利于投机。 - 雪球：该帖提供短线投机风险偏好改善信号，但只有局部活跃和作者短句判断，缺少更强承接验证，按W1记录。（来源：https://xueqiu.com/7143769715/407547568）
+【R3】如果交易能力不足的，这种行情少参与。脆弱性的叠加，如果真遇到利空，本来观望的就多，没有承接力，很容易多杀多，形成踩踏。这... - 雪球：该帖同时具备宏观压力、风格切换、承接不足和多杀多踩踏传导，属于多风险因子共振上升，按R3记录。（来源：https://xueqiu.com/7143769715/407552023）
+【R1】盘面投机性拉满的。听说开始炒作金字辈？ - 雪球：该帖提示情绪和题材投机过热苗头，但正文较短、没有进一步确认承接恶化或亏钱扩散，按R1观察。（来源：https://xueqiu.com/7143769715/407571253）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -702,6 +702,24 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】请问对这种市场有何评论？泥沙俱下，管你利好利空。纯粹筹码博弈。哪怕你站在宏观正确的一面，A股也不会让盈利变得轻松。所以，... - 雪球：该帖具备明确市场对象、触发信息和筹码博弈传导链，作者语气显示风险明显抬升；但没有给出系统性踩踏或多因子共振，按R2记录。（来源：https://xueqiu.com/7143769715/407680501）
+【R2】所以投机反而一往无前。砸一波，贵州燃气封板。这不是2018年熊市的投机开路先锋。机构不是不懂，不砸通胀，跷跷板的科技... - 雪球：该帖同时指出风格跷跷板、诱多和活埋，风险对象和传导清楚；但未达到全市场强风险共振，按R2记录。（来源：https://xueqiu.com/7143769715/407683356）
+【R1】停更了。如果散户能做空盈利，还敢这么嚣张吗。 - 雪球：该帖给出制度不对称的风险苗头，但正文较短、缺少独立验证和更完整市场反馈，按R1观察。（来源：https://xueqiu.com/7143769715/407684336）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -720,6 +720,22 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】加息25基点，落地：单帖同时给出货币政策触发、债务与AI融资传导、人民币汇率反证边界，构成中等风险增强节点；但作者没有给出具体买入、卖出、加仓或减仓指令。（来源：https://xueqiu.com/7143769715/409575102）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险提示" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="风险提示" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -736,6 +736,26 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】CPI引发加息升温，全球科技普跌，存储集中抛售，宏观流动性风险：宏观货币政策风险来源明确（CPI→加息预期），传导链完整且多环节已实际观察到（全球科技普跌、存储集中抛售、韩国限制卖出），判定为进行中的流动性风险增强节点（来源：https://www.xueqiu.com/7143769715/412345157）
+【R2】美债长端利率剧烈波动，AI融资为核心传导变量，存储遭全球集中做空：风险来源（AI相关信贷与杠杆、市场资金供需）与传导链在作者原文中有明确阐述，存储领跌与全球集中做空环节已观察；资本开支停滞与经济衰退环节为条件推断，传导完整度支持R2（来源：https://www.xueqiu.com/7143769715/412385351）
+【R3】美债利率改变估值锚点，AI融资过热与债市股市跷跷板：传导机制（股债跷跷板、估值锚）在作者体系中有明确阐述并与当日利率波动观察相互印证，但当前利率方向混杂（当日利率实际下行、通胀仍顽固），触发未定向，按传导完整度定R3（来源：https://www.xueqiu.com/7143769715/412395417）
+【R2】利率加息影响已反应指数，多杀多扭转颓势困难，中期选举存变数：多杀多与单边趋势为作者当日已观察的市场状态，传导链（承接不足→颓势延续）与政策不确定性来源均有正文证据，判定R2（来源：https://www.xueqiu.com/7143769715/412398226）
+【W3】9月月报说明：通胀顽固、加息周期，据此在创业板点位买入：风险减弱/转向机会节点：来源（点位出清+政策窗口）与传导链（建仓行为+选举政策兑现）有作者正文与评论双重证据；机会依赖中期选举政策兑现，属条件性，定W3（来源：https://www.xueqiu.com/7143769715/412446135）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -756,6 +756,26 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【W2】今日众多产业驱动上涨，依旧是马斯克带的科技潮流：作者观察到权重企稳与创业板多时段金叉，题材驱动与技术面修复同时出现，构成短线风险减弱/转向机会节点；但原帖同时提示早盘高开低走与科技短线兑现，属机会中的反证边界，不改变本次机会判定。（来源：https://www.xueqiu.com/7143769715/412589600）
+【W2】阶段底对应低价筹码，只要不再创历史新低就手握不败：作者明确给出阶段底假设下的持有逻辑与失效条件（再次创历史新低），构成风险减弱/转向机会节点；阶段底属作者点位判断而非已验证事实，已在此标注为待后续验证边界。（来源：https://www.xueqiu.com/7143769715/412593039）
+【R3】医药崩了带崩指数，市场的脆弱性：传导链在帖内完整闭合（消息→板块崩→指数→基金跟随→集体下跌），且作者直接点名市场脆弱性，属情绪风险与市场结构承接力共振的风险增强节点，定级R3。（来源：https://www.xueqiu.com/7143769715/412625224）
+【R2】沪深300ETF尾盘放量但脆弱与信心匮乏：资金放量属市场结构与资金供需变化，但传导显示放量未能修复承接力，量化砸盘熄灭做多动能，风险增强；因存在资金托市的缓冲分支（ETF放量本身），未升至R3。（来源：https://www.xueqiu.com/7143769715/412631376）
+【R2】股指期货交割日多空大战，盘面托而不举：政策与资金双缺位构成市场结构与资金供需层面的风险增强，传导清楚；因作者未确认底部已破、仍处观察状态，定级R2而非R3。（来源：https://www.xueqiu.com/7143769715/412647944）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
+++ b/tools/bbxm-risk-dashboard/data/冰冰小美风险提示.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -776,6 +776,38 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【R2】宁德时代增收不增利，A股产业投资从高景气回归周期：[自动分析｜冰冰小美每日任务] 五步识别：风险表现=龙头增收不增利、毛利率下降与碳酸锂价格担忧已被作者以财报与期货价格佐证（已观察）；风险类型=基本面风险叠加估值风险，暴露对象为锂电产业链与产业主题投资定价；风险来源=中观产业供需与竞争格局变化（内卷+补贴退出）及地缘供应链扰动；关键变量=毛利率/单车利润、碳酸锂价格、研发与技术壁垒溢价、北美供应链政策；传导链各环节均有原帖事实支撑，判定为已支持的增强节点。影响范围限于产业链及其定价模式而非全市场，且作者同时提示技术壁垒可部分对冲，故定级R2。（来源：https://www.xueqiu.com/7143769715/413240926）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[自动分析｜冰冰小美每日任务]
+【W2】等10-23业绩报，存储费半暂时稳住，做空动能下降：[自动分析｜冰冰小美每日任务] 五步识别：风险表现=多个相互独立的市场与标的同日联袂企稳、做空动能开始下降，为作者直接观察（已观察）；风险类型=此前积累的做空压力与波动风险的减弱节点，暴露对象为科技/存储链持仓者；风险来源=微观业绩事件（存储业绩报）与估值回落共同缓解此前压力；关键变量=10-23业绩报落地情况、会议与指引、做空动能延续性；传导链有多市场并列证据支持，判定为已支持的减弱节点。但作者用词为“暂时稳住”且明确等待后续业绩与指引验证，减弱的持续性未确认，故定级W2而非W1。（来源：https://www.xueqiu.com/7143769715/412869898）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
